--- a/docs/feature-status.xlsx
+++ b/docs/feature-status.xlsx
@@ -613,12 +613,20 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -658,12 +666,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-19</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -699,12 +719,20 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -740,12 +768,20 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -785,12 +821,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-24</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -826,12 +874,20 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -871,12 +927,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -912,12 +980,20 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -953,12 +1029,20 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -994,12 +1078,20 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1039,12 +1131,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1084,12 +1188,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-27</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1129,12 +1245,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-09,E-34</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1170,12 +1298,20 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1211,12 +1347,20 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1256,12 +1400,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-09</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1297,12 +1453,20 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1342,12 +1506,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1383,12 +1559,20 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1424,12 +1608,20 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1469,12 +1661,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1514,12 +1718,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1555,12 +1771,20 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1600,12 +1824,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-21</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1641,12 +1877,20 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1686,12 +1930,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1731,12 +1987,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1772,12 +2040,20 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1813,12 +2089,20 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1858,12 +2142,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1899,12 +2195,20 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1944,12 +2248,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-06</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1989,12 +2305,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2034,12 +2362,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-06</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2075,12 +2415,20 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2120,12 +2468,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2165,12 +2525,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-38</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2210,12 +2582,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-19b</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2251,12 +2635,20 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2292,12 +2684,20 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2337,12 +2737,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2378,12 +2790,20 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2419,12 +2839,20 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2460,12 +2888,20 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2501,12 +2937,20 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2546,12 +2990,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2591,12 +3047,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2636,12 +3104,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-04 documented</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2677,12 +3157,20 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2722,12 +3210,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-26</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2763,12 +3263,20 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="3" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2808,12 +3316,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-25</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2853,12 +3373,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-15b</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2898,12 +3430,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2939,12 +3483,20 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="3" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2984,12 +3536,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-08</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3029,12 +3593,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-29</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3074,12 +3650,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3115,12 +3703,20 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="3" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3156,12 +3752,20 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="3" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3201,12 +3805,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-13</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3246,12 +3862,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-13 documented</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3291,12 +3919,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-30 documented</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3336,12 +3976,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3381,12 +4033,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-39 documented</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3422,12 +4086,20 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3467,12 +4139,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-40</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3512,12 +4196,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-10</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3557,12 +4253,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-10b</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3602,12 +4310,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-26,E-27 documented</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3647,12 +4367,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3688,12 +4420,20 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3733,12 +4473,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>documented: E-24</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3778,12 +4530,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3823,12 +4587,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3868,12 +4644,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3913,12 +4701,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3958,12 +4758,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>partially fixed</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>pass (fixed items); E-48 documented</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4003,12 +4815,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="3" t="inlineStr"/>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05: suites green (memory 216 / core 429+ / agents 33 / mcp 102 / integrations 52 / cli 30, tsc clean)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K80"/>
@@ -4108,8 +4932,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>pass (new regression test: delete_all_survives_a_meeting_with_transcript_and_recap)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4142,8 +4974,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>pass (gate tests x7 + meeting_lifecycle x12; decline recorded on NotNow/Stop, flick no longer wipes, backwards clock re-anchors)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4176,8 +5016,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>pass (GCal/Drive shown Coming soon; connect/fetch rejected for unserved services)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4210,8 +5058,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>read egress traced at wiring (poller + on-demand command); lib-level enforcement deferred</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4244,8 +5100,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>pass (new test: a_corroborated_row_survives_the_next_decay_pass)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4278,8 +5142,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>already traced in product wiring (save_gmail_draft records Composio trace)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4312,8 +5184,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>consent gate added to fetch_on_demand (device-verify pending: macOS-only code)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4346,8 +5226,16 @@
           <t>document (needs shared-queue architecture; fails safe)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>needs shared-queue architecture; fails safe today</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4380,8 +5268,16 @@
           <t>document (design work)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>design work: cold-tier search path</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4414,8 +5310,16 @@
           <t>fix now (minimal UI)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>feature work: action buttons UI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4448,8 +5352,16 @@
           <t>document (feature work)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>feature work: search UI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4482,8 +5394,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>pass (new test: context_actions_excludes_resolved_state)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4516,8 +5436,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>painted/interact/collapse_request now invoked from webview (typecheck pass; device-verify pending)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4550,8 +5478,16 @@
           <t>document (streaming transport is follow-up work)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>streaming transport is planned follow-up</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4584,8 +5520,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90s chat timeout added (typecheck pass)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4618,8 +5562,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>pass (new test: export_covers_meetings_notes_transcripts_and_provenance)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4652,8 +5604,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>capabilities now include fullui+meeting windows + allow-close (device-verify pending)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4686,8 +5646,16 @@
           <t>document (by design until Wave 2)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>by design until Wave 2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4720,8 +5688,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>dead shogun.open write removed; expanded launch kept (deliberate, commented)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4754,8 +5730,16 @@
           <t>fix now (scope by app)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>pass (dedup scoped per app + touch extends thread activity; new tests)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,8 +5772,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>usage text now truthful (env token, no --json/--no-screen claims)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4822,8 +5814,16 @@
           <t>document (design decision pending)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>hover preview design decision pending</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4856,8 +5856,16 @@
           <t>document</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>brief provenance additive schema work</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4890,8 +5898,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>preset() returns Option; no silent fallback to send-capable preset</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4924,8 +5940,16 @@
           <t>document (v1 scope)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>v1 scope</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4958,8 +5982,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>pass (new Disposition::Failed + test)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4992,8 +6024,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>pass (boot-cutoff param; live session cannot be zero-lengthed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5026,8 +6066,16 @@
           <t>document (design work)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>design work: per-position chrome</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5060,8 +6108,16 @@
           <t>fix now (remove stale Gmail direct config)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Gmail direct-MCP config is a deliberate GA contingency (CLAUDE.md)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5094,8 +6150,16 @@
           <t>document (OAuth flow is feature work)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>real OAuth flow is feature work</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5128,8 +6192,16 @@
           <t>document (feature work)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>exclusions settings UI is feature work</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5162,8 +6234,16 @@
           <t>fix now (save on hide)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>note auto-saves (800ms debounce) + falls back to last session id</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5196,8 +6276,16 @@
           <t>merged into E-18</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>merged into E-18</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5230,8 +6318,16 @@
           <t>document (measure first)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>measure before changing</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5264,8 +6360,16 @@
           <t>fix now (move JP copy to strings)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>AnalyticsToggle copy now EN via strings.ts; openPanel shows real shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5298,8 +6402,16 @@
           <t>fix now (region from real panel size)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>R_exp default now 560x360 (panel size); notch tests pass</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -5332,8 +6444,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>secure-field skips charged to element budget</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5366,8 +6486,16 @@
           <t>fix now (route label)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>route fallback unreachable (DB CHECK); .ok() swallowing is crash-resistance design</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5400,8 +6528,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>opened_at = evidence ts (backfill staleness honest)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -5434,8 +6570,16 @@
           <t>fix now (summaries)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>summaries labelled 'summary (unverified):', never naked facts</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5468,8 +6612,16 @@
           <t>fix now (log failures)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>ledger write failures logged</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5502,8 +6654,16 @@
           <t>document</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>run_dream_now blocking + client-side batch key flagged in code</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5536,8 +6696,16 @@
           <t>document (privacy note)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>privacy note: chat history in localStorage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5570,8 +6738,16 @@
           <t>document</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>undo/poll polish backlog</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5604,8 +6780,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>key_rejected clears on next successful completion</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5638,8 +6822,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>silence signal fed from audio lane last_voice_ms</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5672,8 +6864,16 @@
           <t>fix now (wire or remove)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>fix-links navigate panes; dead Why?/Review buttons replaced; Run now wired</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5706,8 +6906,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>clock() applies OS local offset</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5740,8 +6948,16 @@
           <t>fix now (default pane)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>default pane = Today; no-refresh + plan hardcode documented</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5774,8 +6990,16 @@
           <t>fix now</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>appearance JSON-parsed in onboarding</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5808,8 +7032,16 @@
           <t>fix now (add settings section)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Usage analytics section added to panel Settings</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5842,8 +7074,16 @@
           <t>document</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>getter side-effect backlog</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5876,8 +7116,16 @@
           <t>document (cleanup backlog)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>dead-code cleanup backlog</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H54"/>
